--- a/CDF_Template.xlsx
+++ b/CDF_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37e8bf313699c053/Samaritan's Purse/apprentice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larrington/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{547402FC-7068-4702-A950-329064AD0D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D2F42E-DDE0-9B4F-B305-BA1D2F878542}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B6059EE-1B5B-8247-BC13-120B63BE4F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="13600" windowHeight="15560" xr2:uid="{DFCFC3C2-3019-4FCB-9E60-88B081D83644}"/>
   </bookViews>
@@ -1724,7 +1724,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1774,10 +1774,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1890,23 +1886,517 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="27" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1926,39 +2416,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2006,18 +2464,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2026,494 +2472,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="27" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2831,7 +2791,7 @@
   <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="31" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="35.1640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="4" customWidth="1"/>
@@ -2839,10 +2799,10 @@
     <col min="6" max="6" width="13.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="7.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="22" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="23" customWidth="1"/>
-    <col min="11" max="11" width="3.5" style="22" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="22" customWidth="1"/>
+    <col min="11" max="11" width="3.5" style="21" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="22" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.1640625" style="4"/>
     <col min="14" max="14" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.1640625" style="4"/>
@@ -2853,360 +2813,360 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="167" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="169" t="s">
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
       <c r="L1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="178"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="170" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="173" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="170" t="s">
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="170"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="158"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="158"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160"/>
-      <c r="K4" s="160"/>
-      <c r="L4" s="161"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="158" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="165"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="166"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="122" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="122"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="61"/>
+      <c r="H6" s="28" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" s="8" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="158" t="s">
+      <c r="B7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="184"/>
-      <c r="K7" s="184"/>
-      <c r="L7" s="185"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="193" t="s">
+      <c r="A8" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="195" t="s">
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="196"/>
-      <c r="F8" s="197" t="s">
+      <c r="E8" s="69"/>
+      <c r="F8" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="195"/>
-      <c r="H8" s="195"/>
-      <c r="I8" s="195"/>
-      <c r="J8" s="195"/>
-      <c r="K8" s="196"/>
-      <c r="L8" s="198" t="s">
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="49" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="199"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="192"/>
-      <c r="E9" s="192"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="60"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="84"/>
     </row>
     <row r="10" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="60"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="84"/>
     </row>
     <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="192"/>
-      <c r="E11" s="192"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="60"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="84"/>
     </row>
     <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="192"/>
-      <c r="E12" s="192"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="60"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="84"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="60"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="84"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="60"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="84"/>
     </row>
     <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="78"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="60"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="84"/>
     </row>
     <row r="16" spans="1:12" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="192"/>
-      <c r="E16" s="192"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="60"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="84"/>
     </row>
     <row r="17" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="192"/>
-      <c r="E17" s="192"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="60"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
+      <c r="L17" s="84"/>
     </row>
     <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="146" t="s">
+      <c r="A18" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="192"/>
-      <c r="E18" s="192"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="60"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="84"/>
     </row>
     <row r="19" spans="1:12" ht="32" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="149" t="s">
+      <c r="A19" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="150"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="200"/>
-      <c r="E19" s="200"/>
-      <c r="F19" s="201"/>
-      <c r="G19" s="201"/>
-      <c r="H19" s="201"/>
-      <c r="I19" s="201"/>
-      <c r="J19" s="201"/>
-      <c r="K19" s="201"/>
-      <c r="L19" s="28"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="27"/>
     </row>
     <row r="20" spans="1:12" s="9" customFormat="1" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="146" t="s">
+      <c r="A20" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="186" t="s">
+      <c r="B20" s="86"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="172" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="148"/>
-      <c r="F20" s="187" t="s">
+      <c r="E20" s="87"/>
+      <c r="F20" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="187" t="s">
+      <c r="H20" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="188" t="s">
+      <c r="I20" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="189" t="s">
+      <c r="J20" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="190"/>
-      <c r="L20" s="191" t="s">
+      <c r="K20" s="95"/>
+      <c r="L20" s="48" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3214,19 +3174,19 @@
       <c r="A21" s="10">
         <v>1</v>
       </c>
-      <c r="B21" s="144"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
+      <c r="B21" s="191"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="104"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="26"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="136">
+      <c r="I21" s="44"/>
+      <c r="J21" s="96">
         <v>0</v>
       </c>
-      <c r="K21" s="137"/>
-      <c r="L21" s="14">
+      <c r="K21" s="97"/>
+      <c r="L21" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3234,19 +3194,19 @@
       <c r="A22" s="10">
         <v>2</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="104"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="26"/>
+      <c r="G22" s="25"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="136">
+      <c r="I22" s="44"/>
+      <c r="J22" s="96">
         <v>0</v>
       </c>
-      <c r="K22" s="137"/>
-      <c r="L22" s="14">
+      <c r="K22" s="97"/>
+      <c r="L22" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3254,19 +3214,19 @@
       <c r="A23" s="10">
         <v>3</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="104"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="26"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="12"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="136">
+      <c r="I23" s="44"/>
+      <c r="J23" s="96">
         <v>0</v>
       </c>
-      <c r="K23" s="137"/>
-      <c r="L23" s="14">
+      <c r="K23" s="97"/>
+      <c r="L23" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3274,19 +3234,19 @@
       <c r="A24" s="10">
         <v>4</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="104"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="26"/>
+      <c r="G24" s="25"/>
       <c r="H24" s="12"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="136">
+      <c r="I24" s="44"/>
+      <c r="J24" s="96">
         <v>0</v>
       </c>
-      <c r="K24" s="137"/>
-      <c r="L24" s="14">
+      <c r="K24" s="97"/>
+      <c r="L24" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3294,19 +3254,19 @@
       <c r="A25" s="10">
         <v>5</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="47"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="104"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="26"/>
+      <c r="G25" s="25"/>
       <c r="H25" s="12"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="136">
+      <c r="I25" s="44"/>
+      <c r="J25" s="96">
         <v>0</v>
       </c>
-      <c r="K25" s="137"/>
-      <c r="L25" s="14">
+      <c r="K25" s="97"/>
+      <c r="L25" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3314,19 +3274,19 @@
       <c r="A26" s="10">
         <v>6</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="104"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="26"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="136">
+      <c r="I26" s="44"/>
+      <c r="J26" s="96">
         <v>0</v>
       </c>
-      <c r="K26" s="137"/>
-      <c r="L26" s="14">
+      <c r="K26" s="97"/>
+      <c r="L26" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3334,19 +3294,19 @@
       <c r="A27" s="10">
         <v>7</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="104"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="26"/>
+      <c r="G27" s="25"/>
       <c r="H27" s="12"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="136">
+      <c r="I27" s="44"/>
+      <c r="J27" s="96">
         <v>0</v>
       </c>
-      <c r="K27" s="137"/>
-      <c r="L27" s="14">
+      <c r="K27" s="97"/>
+      <c r="L27" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3354,19 +3314,19 @@
       <c r="A28" s="10">
         <v>8</v>
       </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="47"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="104"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="26"/>
+      <c r="G28" s="25"/>
       <c r="H28" s="12"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="136">
+      <c r="I28" s="44"/>
+      <c r="J28" s="96">
         <v>0</v>
       </c>
-      <c r="K28" s="137"/>
-      <c r="L28" s="14">
+      <c r="K28" s="97"/>
+      <c r="L28" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3374,21 +3334,21 @@
       <c r="A29" s="10">
         <v>9</v>
       </c>
-      <c r="B29" s="134" t="s">
+      <c r="B29" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="135"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="47"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="104"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="26"/>
+      <c r="G29" s="25"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="136">
+      <c r="I29" s="44"/>
+      <c r="J29" s="96">
         <v>0</v>
       </c>
-      <c r="K29" s="137"/>
-      <c r="L29" s="14">
+      <c r="K29" s="97"/>
+      <c r="L29" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3396,646 +3356,525 @@
       <c r="A30" s="10">
         <v>10</v>
       </c>
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="135"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="47"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="104"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="26"/>
+      <c r="G30" s="25"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="136">
+      <c r="I30" s="44"/>
+      <c r="J30" s="96">
         <v>0</v>
       </c>
-      <c r="K30" s="137"/>
-      <c r="L30" s="14">
+      <c r="K30" s="97"/>
+      <c r="L30" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="8" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="39">
+      <c r="A31" s="38">
         <v>11</v>
       </c>
-      <c r="B31" s="138" t="s">
+      <c r="B31" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="139"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
       <c r="I31" s="43"/>
-      <c r="J31" s="140">
+      <c r="J31" s="105">
         <v>0</v>
       </c>
-      <c r="K31" s="141"/>
-      <c r="L31" s="36">
+      <c r="K31" s="106"/>
+      <c r="L31" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="8" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="117" t="s">
+      <c r="A32" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="118"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="120" t="s">
+      <c r="B32" s="110"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="121"/>
-      <c r="L32" s="15" t="s">
+      <c r="K32" s="113"/>
+      <c r="L32" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="122" t="s">
+      <c r="B33" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="122"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="122"/>
-      <c r="G33" s="122"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="124" t="s">
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="114"/>
+      <c r="J33" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="125"/>
-      <c r="L33" s="126"/>
+      <c r="K33" s="116"/>
+      <c r="L33" s="117"/>
     </row>
     <row r="34" spans="1:12" s="8" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="31"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="123"/>
-      <c r="J34" s="124"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="126"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="115"/>
+      <c r="K34" s="116"/>
+      <c r="L34" s="117"/>
     </row>
     <row r="35" spans="1:12" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="127" t="s">
+      <c r="A35" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="129"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="119"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="120"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="78"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="77" t="s">
+      <c r="B36" s="89"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="74"/>
-      <c r="L36" s="79" t="s">
+      <c r="E36" s="89"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="122" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="130" t="s">
+      <c r="A37" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="131"/>
-      <c r="C37" s="131"/>
-      <c r="D37" s="132" t="s">
+      <c r="B37" s="125"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="131"/>
-      <c r="F37" s="131"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="131"/>
-      <c r="J37" s="131"/>
-      <c r="K37" s="133"/>
-      <c r="L37" s="80"/>
+      <c r="E37" s="125"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="125"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="123"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="96"/>
-      <c r="B38" s="97"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="102"/>
+      <c r="A38" s="128"/>
+      <c r="B38" s="129"/>
+      <c r="C38" s="130"/>
+      <c r="D38" s="134"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="135"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="140"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="99"/>
-      <c r="B39" s="100"/>
-      <c r="C39" s="101"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="102"/>
+      <c r="A39" s="131"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="133"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="138"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="139"/>
+      <c r="L39" s="140"/>
     </row>
     <row r="40" spans="1:12" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="103" t="s">
+      <c r="A40" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="104"/>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="105"/>
+      <c r="B40" s="142"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="142"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="142"/>
+      <c r="L40" s="143"/>
     </row>
     <row r="41" spans="1:12" ht="32" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="106" t="s">
+      <c r="A41" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="104"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="105"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="142"/>
+      <c r="D41" s="142"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
+      <c r="L41" s="143"/>
     </row>
     <row r="42" spans="1:12" s="8" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="107" t="s">
+      <c r="A42" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="108"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="109"/>
-      <c r="E42" s="110"/>
-      <c r="F42" s="25" t="s">
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
+      <c r="D42" s="147"/>
+      <c r="E42" s="148"/>
+      <c r="F42" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H42" s="108" t="s">
+      <c r="H42" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="I42" s="108"/>
-      <c r="J42" s="16" t="s">
+      <c r="I42" s="146"/>
+      <c r="J42" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="K42" s="113" t="s">
+      <c r="K42" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="L42" s="72"/>
+      <c r="L42" s="152"/>
     </row>
     <row r="43" spans="1:12" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="114"/>
-      <c r="E43" s="111"/>
-      <c r="F43" s="17" t="s">
+      <c r="B43" s="154"/>
+      <c r="C43" s="154"/>
+      <c r="D43" s="155"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G43" s="18"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="90"/>
-      <c r="L43" s="91"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="158"/>
+      <c r="L43" s="159"/>
     </row>
     <row r="44" spans="1:12" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="83"/>
-      <c r="B44" s="84"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="17" t="s">
+      <c r="A44" s="153"/>
+      <c r="B44" s="154"/>
+      <c r="C44" s="154"/>
+      <c r="D44" s="156"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G44" s="18"/>
-      <c r="H44" s="89"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="91"/>
-    </row>
-    <row r="45" spans="1:12" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="115" t="s">
+      <c r="G44" s="17"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="158"/>
+      <c r="L44" s="159"/>
+    </row>
+    <row r="45" spans="1:12" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="116"/>
-      <c r="C45" s="116"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="111"/>
-      <c r="F45" s="17" t="s">
+      <c r="B45" s="161"/>
+      <c r="C45" s="161"/>
+      <c r="D45" s="156"/>
+      <c r="E45" s="149"/>
+      <c r="F45" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="G45" s="18"/>
-      <c r="H45" s="89"/>
-      <c r="I45" s="89"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="90"/>
-      <c r="L45" s="91"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="158"/>
+      <c r="L45" s="159"/>
     </row>
     <row r="46" spans="1:12" s="8" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="115"/>
-      <c r="B46" s="116"/>
-      <c r="C46" s="116"/>
-      <c r="D46" s="95"/>
-      <c r="E46" s="111"/>
-      <c r="F46" s="17" t="s">
+      <c r="A46" s="160"/>
+      <c r="B46" s="161"/>
+      <c r="C46" s="161"/>
+      <c r="D46" s="156"/>
+      <c r="E46" s="149"/>
+      <c r="F46" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G46" s="18"/>
-      <c r="H46" s="89"/>
-      <c r="I46" s="89"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="90"/>
-      <c r="L46" s="91"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="158"/>
+      <c r="L46" s="159"/>
     </row>
     <row r="47" spans="1:12" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="83" t="s">
+      <c r="A47" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="84"/>
-      <c r="C47" s="84"/>
-      <c r="D47" s="95"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="17" t="s">
+      <c r="B47" s="154"/>
+      <c r="C47" s="154"/>
+      <c r="D47" s="156"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G47" s="18"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="90"/>
-      <c r="L47" s="91"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="158"/>
+      <c r="L47" s="159"/>
     </row>
     <row r="48" spans="1:12" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="83"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="95"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="17" t="s">
+      <c r="A48" s="153"/>
+      <c r="B48" s="154"/>
+      <c r="C48" s="154"/>
+      <c r="D48" s="156"/>
+      <c r="E48" s="149"/>
+      <c r="F48" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G48" s="18"/>
-      <c r="H48" s="89"/>
-      <c r="I48" s="89"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="90"/>
-      <c r="L48" s="91"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="157"/>
+      <c r="I48" s="157"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="158"/>
+      <c r="L48" s="159"/>
     </row>
     <row r="49" spans="1:12" s="8" customFormat="1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="83" t="s">
+      <c r="A49" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="84"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="87"/>
-      <c r="E49" s="111"/>
-      <c r="F49" s="17" t="s">
+      <c r="B49" s="154"/>
+      <c r="C49" s="154"/>
+      <c r="D49" s="166"/>
+      <c r="E49" s="149"/>
+      <c r="F49" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="90"/>
-      <c r="L49" s="91"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="157"/>
+      <c r="I49" s="157"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="158"/>
+      <c r="L49" s="159"/>
     </row>
     <row r="50" spans="1:12" s="8" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="85"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="37" t="s">
+      <c r="A50" s="164"/>
+      <c r="B50" s="165"/>
+      <c r="C50" s="165"/>
+      <c r="D50" s="167"/>
+      <c r="E50" s="150"/>
+      <c r="F50" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="38"/>
-      <c r="H50" s="92" t="s">
+      <c r="G50" s="37"/>
+      <c r="H50" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="I50" s="92"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="93" t="s">
+      <c r="I50" s="168"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="L50" s="94"/>
+      <c r="L50" s="170"/>
     </row>
     <row r="51" spans="1:12" s="8" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="32"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
     </row>
     <row r="52" spans="1:12" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="70" t="s">
+      <c r="A52" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="71"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="71"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="71"/>
-      <c r="L52" s="72"/>
+      <c r="B52" s="188"/>
+      <c r="C52" s="188"/>
+      <c r="D52" s="188"/>
+      <c r="E52" s="188"/>
+      <c r="F52" s="188"/>
+      <c r="G52" s="188"/>
+      <c r="H52" s="188"/>
+      <c r="I52" s="188"/>
+      <c r="J52" s="188"/>
+      <c r="K52" s="188"/>
+      <c r="L52" s="152"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="73"/>
-      <c r="B53" s="74"/>
-      <c r="C53" s="77" t="s">
+      <c r="A53" s="88"/>
+      <c r="B53" s="90"/>
+      <c r="C53" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="D53" s="74"/>
-      <c r="E53" s="77" t="s">
+      <c r="D53" s="90"/>
+      <c r="E53" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="78"/>
-      <c r="G53" s="78"/>
-      <c r="H53" s="78"/>
-      <c r="I53" s="78"/>
-      <c r="J53" s="78"/>
-      <c r="K53" s="74"/>
-      <c r="L53" s="79" t="s">
+      <c r="F53" s="89"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="89"/>
+      <c r="J53" s="89"/>
+      <c r="K53" s="90"/>
+      <c r="L53" s="122" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="75"/>
-      <c r="B54" s="76"/>
-      <c r="C54" s="81" t="s">
+      <c r="A54" s="189"/>
+      <c r="B54" s="190"/>
+      <c r="C54" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="D54" s="82"/>
-      <c r="E54" s="81" t="s">
+      <c r="D54" s="163"/>
+      <c r="E54" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="80"/>
+      <c r="F54" s="163"/>
+      <c r="G54" s="163"/>
+      <c r="H54" s="163"/>
+      <c r="I54" s="163"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="163"/>
+      <c r="L54" s="123"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="48" t="s">
+      <c r="A55" s="173" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="49"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="55"/>
-      <c r="L55" s="59"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="134"/>
+      <c r="F55" s="135"/>
+      <c r="G55" s="135"/>
+      <c r="H55" s="135"/>
+      <c r="I55" s="135"/>
+      <c r="J55" s="135"/>
+      <c r="K55" s="136"/>
+      <c r="L55" s="177"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="48"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="58"/>
-      <c r="L56" s="60"/>
+      <c r="A56" s="173"/>
+      <c r="B56" s="174"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="138"/>
+      <c r="G56" s="138"/>
+      <c r="H56" s="138"/>
+      <c r="I56" s="138"/>
+      <c r="J56" s="138"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="84"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="48" t="s">
+      <c r="A57" s="173" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="49"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="67"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="60"/>
+      <c r="B57" s="174"/>
+      <c r="C57" s="180"/>
+      <c r="D57" s="181"/>
+      <c r="E57" s="180"/>
+      <c r="F57" s="184"/>
+      <c r="G57" s="184"/>
+      <c r="H57" s="184"/>
+      <c r="I57" s="184"/>
+      <c r="J57" s="184"/>
+      <c r="K57" s="181"/>
+      <c r="L57" s="84"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="61"/>
-      <c r="B58" s="62"/>
-      <c r="C58" s="65"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="66"/>
-      <c r="L58" s="69"/>
+      <c r="A58" s="178"/>
+      <c r="B58" s="179"/>
+      <c r="C58" s="182"/>
+      <c r="D58" s="183"/>
+      <c r="E58" s="182"/>
+      <c r="F58" s="185"/>
+      <c r="G58" s="185"/>
+      <c r="H58" s="185"/>
+      <c r="I58" s="185"/>
+      <c r="J58" s="185"/>
+      <c r="K58" s="183"/>
+      <c r="L58" s="186"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59" s="45"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
-      <c r="L59" s="45"/>
+      <c r="A59" s="171"/>
+      <c r="B59" s="171"/>
+      <c r="C59" s="171"/>
+      <c r="D59" s="171"/>
+      <c r="E59" s="171"/>
+      <c r="F59" s="171"/>
+      <c r="G59" s="171"/>
+      <c r="H59" s="171"/>
+      <c r="I59" s="171"/>
+      <c r="J59" s="171"/>
+      <c r="K59" s="171"/>
+      <c r="L59" s="171"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" selectLockedCells="1" sort="0"/>
   <mergeCells count="145">
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="F9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="F13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E18"/>
-    <mergeCell ref="F17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B33:I34"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="D38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:E50"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="A45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="K48:L48"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
@@ -4060,6 +3899,127 @@
     <mergeCell ref="E53:K53"/>
     <mergeCell ref="L53:L54"/>
     <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="D38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:E50"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B33:I34"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:K37"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E18"/>
+    <mergeCell ref="F17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="F13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="F9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:K8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Please enter an 'X' if item is taxable, or leave BLANK if non-taxable." sqref="I21:I31" xr:uid="{B7093725-9997-4EBC-B647-A19967A14D48}">
